--- a/backend/data/financials_by_company/1BHA.F.xlsx
+++ b/backend/data/financials_by_company/1BHA.F.xlsx
@@ -3344,10 +3344,8 @@
           <t>NSW</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
+      <c r="D2" t="n">
+        <v>2000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3605,7 +3603,7 @@
         <v>0.228</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
         <v>-0.09449001</v>
